--- a/assemblies-and-events/valentines-day-sweet-notes/downloads/Valentines_Day_Sweet_Notes_Tracker.xlsx
+++ b/assemblies-and-events/valentines-day-sweet-notes/downloads/Valentines_Day_Sweet_Notes_Tracker.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">      Sweet Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">      A Valentines event, built on kindness     |     The Pastoral Guide</t>
+    <t xml:space="preserve">      A Valentine’s event, built on kindness     |     The Pastoral Guide</t>
   </si>
   <si>
     <t xml:space="preserve">Fill these in first</t>
